--- a/data/trending_integrated_20261028_11.xlsx
+++ b/data/trending_integrated_20261028_11.xlsx
@@ -578,13 +578,13 @@
         <v>-0.19</v>
       </c>
       <c r="E2" t="n">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="F2" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G2" t="n">
-        <v>163</v>
+        <v>199</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -610,7 +610,7 @@
         <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>145255215436</v>
+        <v>147137801391</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 기대감 형성. 27일 애프터 종가 기준으로 매물대 돌파 시 추가 상승 전망.</t>
+          <t>빛과전자, 광통신주 강세 및 갭 상승 마감. 쓰레기 회사 인식 극복 및 상한가 기대감 형성.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광통신', '미국 시장', '매물대']</t>
+          <t>['광통신', '갭상승', '상한가']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29000</v>
+        <v>29050</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.11%</t>
+          <t>'+22.32%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F3" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="H3" t="n">
         <v>5.16</v>
@@ -702,7 +702,7 @@
         <v>5.31</v>
       </c>
       <c r="O3" t="n">
-        <v>131297818575</v>
+        <v>134211391150</v>
       </c>
       <c r="P3" t="n">
         <v>50600</v>
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>나무가</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19180</v>
+        <v>18070</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+12.23%</t>
+          <t>'+14.15%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.61</v>
+        <v>1.02</v>
       </c>
       <c r="E4" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="F4" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G4" t="n">
-        <v>271</v>
+        <v>214</v>
       </c>
       <c r="H4" t="n">
-        <v>4.74</v>
+        <v>1.11</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>17090</v>
+        <v>15830</v>
       </c>
       <c r="K4" t="n">
-        <v>19270</v>
+        <v>17170</v>
       </c>
       <c r="L4" t="n">
-        <v>20450</v>
+        <v>18530</v>
       </c>
       <c r="M4" t="n">
-        <v>18070</v>
+        <v>15830</v>
       </c>
       <c r="N4" t="n">
-        <v>4.13</v>
+        <v>0.09</v>
       </c>
       <c r="O4" t="n">
-        <v>37307506640</v>
+        <v>189497604790</v>
       </c>
       <c r="P4" t="n">
-        <v>28600</v>
+        <v>28800</v>
       </c>
       <c r="Q4" t="n">
-        <v>11050</v>
+        <v>11550</v>
       </c>
       <c r="R4" t="n">
-        <v>-34000</v>
+        <v>-21000</v>
       </c>
       <c r="S4" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>나무가, 미국 휴머노이드 로봇 '아틀라스' 1만대 발주 관련 수혜 기대. 삼성, 현대차 등 주요 기업들과의 연관성 부각.</t>
+          <t>멜콘, 마이크론 반도체 장비 평가 완료 및 ASML 공급망 진입. AI 데이터센터 공급계약, 저평가된 시가총액 및 반도체 대장주로서의 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['휴머노이드', '로봇 부품', '아틀라스']</t>
+          <t>['마이크론', 'AI', '공급계약']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>190510</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>나무가</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17530</v>
+        <v>19000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.74%</t>
+          <t>'+11.18%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.02</v>
+        <v>0.61</v>
       </c>
       <c r="E5" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F5" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G5" t="n">
-        <v>199</v>
+        <v>278</v>
       </c>
       <c r="H5" t="n">
-        <v>1.11</v>
+        <v>4.74</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>15830</v>
+        <v>17090</v>
       </c>
       <c r="K5" t="n">
-        <v>17170</v>
+        <v>19270</v>
       </c>
       <c r="L5" t="n">
-        <v>18530</v>
+        <v>20450</v>
       </c>
       <c r="M5" t="n">
-        <v>15830</v>
+        <v>18070</v>
       </c>
       <c r="N5" t="n">
-        <v>0.09</v>
+        <v>4.13</v>
       </c>
       <c r="O5" t="n">
-        <v>178214213270</v>
+        <v>37832691455</v>
       </c>
       <c r="P5" t="n">
-        <v>28800</v>
+        <v>28600</v>
       </c>
       <c r="Q5" t="n">
-        <v>11550</v>
+        <v>11050</v>
       </c>
       <c r="R5" t="n">
-        <v>-21000</v>
+        <v>-34000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 마이크론 반도체 장비 평가 완료 및 ASML 공급망 진입 뉴스 부각. AI 데이터센터 방열시스템 공급 계약으로 밸류에이션 재평가 기대.</t>
+          <t>나무가, 아틀라스 휴머노이드 발주 및 로봇 부품 대장주로서의 입지 강화. 삼성, 구글, 현대차 등과의 협력 및 매년 300억대 이익 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['마이크론', 'ASML', '방열시스템']</t>
+          <t>['휴머노이드', '로봇부품', '아틀라스']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,169 +924,169 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>190510</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>188600</v>
+        <v>15190</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.23%</t>
+          <t>'+10.88%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="F6" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>201</v>
+        <v>343</v>
       </c>
       <c r="H6" t="n">
-        <v>74.90000000000001</v>
+        <v>2.87</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>171100</v>
+        <v>13700</v>
       </c>
       <c r="K6" t="n">
-        <v>176300</v>
+        <v>14210</v>
       </c>
       <c r="L6" t="n">
-        <v>189000</v>
+        <v>15290</v>
       </c>
       <c r="M6" t="n">
-        <v>175400</v>
+        <v>14210</v>
       </c>
       <c r="N6" t="n">
-        <v>74.89</v>
+        <v>2.82</v>
       </c>
       <c r="O6" t="n">
-        <v>464043561500</v>
+        <v>120046377105</v>
       </c>
       <c r="P6" t="n">
-        <v>243500</v>
+        <v>31500</v>
       </c>
       <c r="Q6" t="n">
-        <v>71000</v>
+        <v>1760</v>
       </c>
       <c r="R6" t="n">
-        <v>654000</v>
+        <v>247000</v>
       </c>
       <c r="S6" t="n">
-        <v>-1000</v>
+        <v>3000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성전자우, 외국인 매수세 및 숏 스퀴즈 가능성 언급. 자사주 매입 기대.</t>
+          <t>대한광통신, 메타 유리 기판 및 해상광통신 케이블 관련 기대감. 외인 프로그램 매수세 유입 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['숏 스퀴즈', '자사주매입', '우선주']</t>
+          <t>['해상광통신', '유리기판', '외인매수']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2685</v>
+        <v>187200</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.59%</t>
+          <t>'+9.41%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.68</v>
+        <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F7" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G7" t="n">
-        <v>58</v>
+        <v>218</v>
       </c>
       <c r="H7" t="n">
-        <v>1.69</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2450</v>
+        <v>171100</v>
       </c>
       <c r="K7" t="n">
-        <v>2525</v>
+        <v>176300</v>
       </c>
       <c r="L7" t="n">
-        <v>2965</v>
+        <v>189000</v>
       </c>
       <c r="M7" t="n">
-        <v>2505</v>
+        <v>175400</v>
       </c>
       <c r="N7" t="n">
-        <v>1.01</v>
+        <v>74.89</v>
       </c>
       <c r="O7" t="n">
-        <v>60811473257</v>
+        <v>475348126150</v>
       </c>
       <c r="P7" t="n">
-        <v>2965</v>
+        <v>243500</v>
       </c>
       <c r="Q7" t="n">
-        <v>865</v>
+        <v>71000</v>
       </c>
       <c r="R7" t="n">
-        <v>181000</v>
+        <v>654000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈, 미국 1000억원 규모 하이브리드 부품 수주 및 개인 물량 흡수 후 상승 기대.</t>
+          <t>삼성전자우, 외국인 매수세 및 숏 스퀴즈 가능성 언급. 자사주 매입 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['수주', '하이브리드', '부품']</t>
+          <t>['숏 스퀴즈', '자사주매입', '우선주']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14970</v>
+        <v>1447000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+9.27%</t>
+          <t>'+7.90%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>81</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>39</v>
+        <v>477</v>
       </c>
       <c r="G8" t="n">
-        <v>287</v>
+        <v>1836</v>
       </c>
       <c r="H8" t="n">
-        <v>2.87</v>
+        <v>48.61</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>13700</v>
+        <v>1341000</v>
       </c>
       <c r="K8" t="n">
-        <v>14210</v>
+        <v>1390000</v>
       </c>
       <c r="L8" t="n">
-        <v>15060</v>
+        <v>1467000</v>
       </c>
       <c r="M8" t="n">
-        <v>14210</v>
+        <v>1358000</v>
       </c>
       <c r="N8" t="n">
-        <v>2.82</v>
+        <v>48.66</v>
       </c>
       <c r="O8" t="n">
-        <v>99089959870</v>
+        <v>2947398166500</v>
       </c>
       <c r="P8" t="n">
-        <v>31500</v>
+        <v>2987000</v>
       </c>
       <c r="Q8" t="n">
-        <v>1760</v>
+        <v>501000</v>
       </c>
       <c r="R8" t="n">
-        <v>247000</v>
+        <v>53000</v>
       </c>
       <c r="S8" t="n">
-        <v>3000</v>
+        <v>55000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>메타버스 유리기판, 해상 광통신 케이블 관련 기대감 및 외인 프로그램 매수세 유입. 공매도 세력에 대한 경계와 함께 대세 상승 전망.</t>
+          <t>SK하이닉스, 2029년까지 HBM 사실상 완판 전망 및 자사주 20조 취득. 긍정적인 컨퍼런스콜 내용과 주가 상승 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['메타버스', '광통신', '외인 매수']</t>
+          <t>['HBM', '완판', '자사주']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1457000</v>
+        <v>239500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.65%</t>
+          <t>'+7.88%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="E9" t="n">
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="G9" t="n">
-        <v>1824</v>
+        <v>1729</v>
       </c>
       <c r="H9" t="n">
-        <v>48.61</v>
+        <v>46.15</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,47 +1239,47 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1341000</v>
+        <v>222000</v>
       </c>
       <c r="K9" t="n">
-        <v>1390000</v>
+        <v>231000</v>
       </c>
       <c r="L9" t="n">
-        <v>1467000</v>
+        <v>243000</v>
       </c>
       <c r="M9" t="n">
-        <v>1358000</v>
+        <v>228000</v>
       </c>
       <c r="N9" t="n">
-        <v>48.66</v>
+        <v>46.1</v>
       </c>
       <c r="O9" t="n">
-        <v>2806848398500</v>
+        <v>1899989386500</v>
       </c>
       <c r="P9" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>501000</v>
+        <v>94500</v>
       </c>
       <c r="R9" t="n">
-        <v>53000</v>
+        <v>1304000</v>
       </c>
       <c r="S9" t="n">
-        <v>55000</v>
+        <v>524000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2029년 반도체 업황 완판 전망 및 컨퍼런스콜 호평. 자사주 20조 취득 발표로 주가 상승 기대감 고조.</t>
+          <t>삼성전자, HBM4 점유율 경쟁 및 26만 전자 가능성 언급. 긍정적 시장 전망과 더불어 매수 추천 의견 존재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['컨퍼런스콜', '자사주', '반도체 업황']</t>
+          <t>['HBM4', '점유율', '매수']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,130 +1292,130 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>241000</v>
+        <v>8760</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+8.56%</t>
+          <t>'+6.83%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.05</v>
+        <v>0.27</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>60</v>
       </c>
       <c r="F10" t="n">
-        <v>470</v>
+        <v>47</v>
       </c>
       <c r="G10" t="n">
-        <v>1836</v>
+        <v>71</v>
       </c>
       <c r="H10" t="n">
-        <v>46.15</v>
+        <v>1.42</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>222000</v>
+        <v>8200</v>
       </c>
       <c r="K10" t="n">
-        <v>231000</v>
+        <v>8230</v>
       </c>
       <c r="L10" t="n">
-        <v>243000</v>
+        <v>9050</v>
       </c>
       <c r="M10" t="n">
-        <v>228000</v>
+        <v>8100</v>
       </c>
       <c r="N10" t="n">
-        <v>46.1</v>
+        <v>1.15</v>
       </c>
       <c r="O10" t="n">
-        <v>1775426221000</v>
+        <v>48493999880</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>9820</v>
       </c>
       <c r="Q10" t="n">
-        <v>94500</v>
+        <v>2965</v>
       </c>
       <c r="R10" t="n">
-        <v>1304000</v>
+        <v>-63000</v>
       </c>
       <c r="S10" t="n">
-        <v>524000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>이재명 관련 긍정적 언급과 함께 HBM4 점유율 경쟁 및 배당금 관련 기대감 부각. 그러나 구체적인 근거 제시 부족.</t>
+          <t>샌즈랩, 미국 양자컴퓨터 및 보안주 강세와 국내 IT 보안 사고 뉴스에 따른 관심 증가. AI 시대 보안 중요성 부각.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['HBM4', '배당금', '점유율']</t>
+          <t>['AI 보안', '양자컴퓨터', 'IT 보안']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8670</v>
+        <v>2615</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+5.73%</t>
+          <t>'+6.73%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.27</v>
+        <v>0.68</v>
       </c>
       <c r="E11" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F11" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G11" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H11" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>8200</v>
+        <v>2450</v>
       </c>
       <c r="K11" t="n">
-        <v>8230</v>
+        <v>2525</v>
       </c>
       <c r="L11" t="n">
-        <v>9050</v>
+        <v>2965</v>
       </c>
       <c r="M11" t="n">
-        <v>8100</v>
+        <v>2505</v>
       </c>
       <c r="N11" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="O11" t="n">
-        <v>45081016915</v>
+        <v>65198596019</v>
       </c>
       <c r="P11" t="n">
-        <v>9820</v>
+        <v>2965</v>
       </c>
       <c r="Q11" t="n">
-        <v>2965</v>
+        <v>865</v>
       </c>
       <c r="R11" t="n">
-        <v>-63000</v>
+        <v>181000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>샌즈랩, 미국 양자컴퓨터 및 보안주 강세와 국내 IT 보안 사고 뉴스에 따른 관심 증가. AI 시대 보안 중요성 부각.</t>
+          <t>삼기에너지솔루션즈, 미국 1000억원 규모 하이브리드 부품 수주 및 개인 물량 흡수 후 상승 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['AI 보안', '양자컴퓨터', 'IT 보안']</t>
+          <t>['수주', '하이브리드', '부품']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>183600</v>
+        <v>182800</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+5.34%</t>
+          <t>'+4.88%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="F12" t="n">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="G12" t="n">
-        <v>1363</v>
+        <v>1398</v>
       </c>
       <c r="H12" t="n">
         <v>35.43</v>
@@ -1530,7 +1530,7 @@
         <v>35.49</v>
       </c>
       <c r="O12" t="n">
-        <v>96868222250</v>
+        <v>100011990100</v>
       </c>
       <c r="P12" t="n">
         <v>304000</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>네이버 야간 선물 폭등 및 코어위브 상승에 따른 기대감 형성. 엔비디아의 3대 주주 등극 소식은 있으나, 구체적인 호재 제시 부족.</t>
+          <t>엔비디아의 주요 주주 등극 가능성에 대한 언급과 함께 주가 상승 기대감 표출. 다만, 연기금 매도 및 과거 삼성전자/SK하이닉스와의 비교를 통해 신중론도 제기.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['야간선물', '엔비디아', '코어위브']</t>
+          <t>['엔비디아', '주주', '신중론']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,79 +1575,79 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2240</v>
+        <v>64000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.23%</t>
+          <t>'+2.89%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.18</v>
+        <v>0.57</v>
       </c>
       <c r="E13" t="n">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="F13" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="G13" t="n">
-        <v>159</v>
+        <v>408</v>
       </c>
       <c r="H13" t="n">
-        <v>5.07</v>
+        <v>41.01</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>2170</v>
+        <v>62200</v>
       </c>
       <c r="K13" t="n">
-        <v>2160</v>
+        <v>63000</v>
       </c>
       <c r="L13" t="n">
-        <v>2475</v>
+        <v>64500</v>
       </c>
       <c r="M13" t="n">
-        <v>2155</v>
+        <v>62200</v>
       </c>
       <c r="N13" t="n">
-        <v>4.89</v>
+        <v>40.44</v>
       </c>
       <c r="O13" t="n">
-        <v>39292243035</v>
+        <v>139918003100</v>
       </c>
       <c r="P13" t="n">
-        <v>4980</v>
+        <v>67300</v>
       </c>
       <c r="Q13" t="n">
-        <v>774</v>
+        <v>23150</v>
       </c>
       <c r="R13" t="n">
-        <v>439000</v>
+        <v>337000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>로봇 섹터 강세 속 앤로보틱스 주가 움직임에 대한 기대와 우려가 공존. 자사주 매도 및 신용 증가 등 혼조세.</t>
+          <t>삼성E&amp;A, 코스피 수익률 1위 달성 및 프로그램 매수세 유입. 추세 전환 가능성과 자사주 매입 기대감 표출.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['로봇 섹터', '신용 증가', '자사주 매도']</t>
+          <t>['수익률', '프로그램매수', '자사주매입']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1655,43 +1655,43 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>64200</v>
+        <v>30350</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+3.22%</t>
+          <t>'+2.88%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.57</v>
+        <v>-0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F14" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G14" t="n">
-        <v>369</v>
+        <v>255</v>
       </c>
       <c r="H14" t="n">
-        <v>41.01</v>
+        <v>28.81</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,130 +1699,130 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>62200</v>
+        <v>29500</v>
       </c>
       <c r="K14" t="n">
-        <v>63000</v>
+        <v>29900</v>
       </c>
       <c r="L14" t="n">
-        <v>64500</v>
+        <v>30650</v>
       </c>
       <c r="M14" t="n">
-        <v>62200</v>
+        <v>29900</v>
       </c>
       <c r="N14" t="n">
-        <v>40.44</v>
+        <v>28.82</v>
       </c>
       <c r="O14" t="n">
-        <v>134973737100</v>
+        <v>22314833900</v>
       </c>
       <c r="P14" t="n">
-        <v>67300</v>
+        <v>69700</v>
       </c>
       <c r="Q14" t="n">
-        <v>23150</v>
+        <v>29200</v>
       </c>
       <c r="R14" t="n">
-        <v>337000</v>
+        <v>120000</v>
       </c>
       <c r="S14" t="n">
-        <v>18000</v>
+        <v>14000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>이란 전쟁 종전 기대감 및 국제유가 하락 속 코스피 수익률 1위 달성. 자사주 매입 예정으로 추가 상승 기대.</t>
+          <t>카카오, 주가 하락세 지속 및 낮은 적정 가치에 대한 부정적 의견. 거래량 부진 시 추가 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['전쟁 종전', '자사주 매입', '수익률']</t>
+          <t>['적정주가', '하락세', '거래량']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>035720</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30450</v>
+        <v>2225</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+3.22%</t>
+          <t>'+2.53%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.01</v>
+        <v>0.18</v>
       </c>
       <c r="E15" t="n">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="F15" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="G15" t="n">
-        <v>255</v>
+        <v>167</v>
       </c>
       <c r="H15" t="n">
-        <v>28.81</v>
+        <v>5.07</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>29500</v>
+        <v>2170</v>
       </c>
       <c r="K15" t="n">
-        <v>29900</v>
+        <v>2160</v>
       </c>
       <c r="L15" t="n">
-        <v>30650</v>
+        <v>2475</v>
       </c>
       <c r="M15" t="n">
-        <v>29900</v>
+        <v>2155</v>
       </c>
       <c r="N15" t="n">
-        <v>28.82</v>
+        <v>4.89</v>
       </c>
       <c r="O15" t="n">
-        <v>21410307500</v>
+        <v>40384023525</v>
       </c>
       <c r="P15" t="n">
-        <v>69700</v>
+        <v>4980</v>
       </c>
       <c r="Q15" t="n">
-        <v>29200</v>
+        <v>774</v>
       </c>
       <c r="R15" t="n">
-        <v>120000</v>
+        <v>439000</v>
       </c>
       <c r="S15" t="n">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>카카오, 주가 하락세 지속 및 낮은 적정 가치에 대한 부정적 의견. 거래량 부진 시 추가 하락 가능성 언급.</t>
+          <t>로봇 섹터 강세 속 앤로보틱스 주가 움직임에 대한 기대와 우려가 공존. 자사주 매도 및 신용 증가 등 혼조세.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['적정주가', '하락세', '거래량']</t>
+          <t>['로봇 섹터', '신용 증가', '자사주 매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>035720</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16490</v>
+        <v>16440</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.61%</t>
+          <t>'+0.31%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F16" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G16" t="n">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="H16" t="n">
         <v>28.03</v>
@@ -1898,7 +1898,7 @@
         <v>27.96</v>
       </c>
       <c r="O16" t="n">
-        <v>27171807980</v>
+        <v>28923162425</v>
       </c>
       <c r="P16" t="n">
         <v>35350</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>삼성중공업, 조선업 불황 속 목표주가 하향 조정 및 공매도 우려.</t>
+          <t>삼성중공업, 수주 증가세에도 목표주가 하향 조정 및 주가 부진 지적. 외국인, 기관 매수세 속 관망세.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['공매도', '목표주가', '조선주']</t>
+          <t>['수주', '목표주가', '외국인매수']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52600</v>
+        <v>52100</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-0.75%</t>
+          <t>'-1.70%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.03</v>
       </c>
       <c r="E17" t="n">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="F17" t="n">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="G17" t="n">
-        <v>803</v>
+        <v>830</v>
       </c>
       <c r="H17" t="n">
         <v>10.31</v>
@@ -1990,7 +1990,7 @@
         <v>10.34</v>
       </c>
       <c r="O17" t="n">
-        <v>47271603400</v>
+        <v>49161968250</v>
       </c>
       <c r="P17" t="n">
         <v>154800</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>한화오션, 미 해군 상륙함 건조 제안서 제출 소식 및 코스피 지수 상승에 따른 반등 기대.</t>
+          <t>한화오션, 코스피 지수 상승에도 주가 하락 및 외국인 매도세. 자사주 매입 및 잠수함 관련 긍정적 뉴스에도 부정적 전망.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['상륙함', '건조', '공매']</t>
+          <t>['잠수함', '외국인매도', '자사주매입']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14230</v>
+        <v>14160</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-1.52%</t>
+          <t>'-2.01%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="F18" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G18" t="n">
-        <v>265</v>
+        <v>297</v>
       </c>
       <c r="H18" t="n">
         <v>9.83</v>
@@ -2076,13 +2076,13 @@
         <v>14870</v>
       </c>
       <c r="M18" t="n">
-        <v>14220</v>
+        <v>14140</v>
       </c>
       <c r="N18" t="n">
         <v>10.02</v>
       </c>
       <c r="O18" t="n">
-        <v>34341408020</v>
+        <v>38640343815</v>
       </c>
       <c r="P18" t="n">
         <v>40350</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>경영진 교체 및 주가 조작 의혹 등 부정적 여론 형성. 외인 매도 및 대차 증가에 따른 하락세 지속 전망.</t>
+          <t>대우건설, 주가조작 및 공매도 의혹 제기. 새 경영진에 대한 불만과 타 건설사 대비 부진한 주가 흐름 지적.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['경영진', '주가 조작', '외인 매도']</t>
+          <t>['주가조작', '공매도', '대차']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2142,13 +2142,13 @@
         <v>0.39</v>
       </c>
       <c r="E19" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F19" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G19" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="H19" t="n">
         <v>2.52</v>
@@ -2174,7 +2174,7 @@
         <v>2.13</v>
       </c>
       <c r="O19" t="n">
-        <v>12378558612</v>
+        <v>12725517317</v>
       </c>
       <c r="P19" t="n">
         <v>6190</v>

--- a/data/trending_integrated_20261028_11.xlsx
+++ b/data/trending_integrated_20261028_11.xlsx
@@ -578,13 +578,13 @@
         <v>-0.19</v>
       </c>
       <c r="E2" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F2" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G2" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -610,7 +610,7 @@
         <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>147137801391</v>
+        <v>147732832776</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>빛과전자, 광통신주 강세 및 갭 상승 마감. 쓰레기 회사 인식 극복 및 상한가 기대감 형성.</t>
+          <t>미국 광통신주 급등, 27일 애프터 종가 3470원 돌파, 갭 15% 상승 등 긍정적인 신호와 함께 상한가 기대감을 보이며, 과거 쓰레기 회사라는 인식에서 벗어나 호재와 미장 상승을 바탕으로 급등 가능성을 제시합니다.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광통신', '갭상승', '상한가']</t>
+          <t>['광통신', '상승', '호재']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29050</v>
+        <v>28800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.32%</t>
+          <t>'+21.26%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F3" t="n">
         <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H3" t="n">
         <v>5.16</v>
@@ -702,7 +702,7 @@
         <v>5.31</v>
       </c>
       <c r="O3" t="n">
-        <v>134211391150</v>
+        <v>135922791700</v>
       </c>
       <c r="P3" t="n">
         <v>50600</v>
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18070</v>
+        <v>9180</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.15%</t>
+          <t>'+11.95%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.02</v>
+        <v>0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="F4" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="G4" t="n">
-        <v>214</v>
+        <v>81</v>
       </c>
       <c r="H4" t="n">
-        <v>1.11</v>
+        <v>1.42</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,91 +779,91 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>15830</v>
+        <v>8200</v>
       </c>
       <c r="K4" t="n">
-        <v>17170</v>
+        <v>8230</v>
       </c>
       <c r="L4" t="n">
-        <v>18530</v>
+        <v>9190</v>
       </c>
       <c r="M4" t="n">
-        <v>15830</v>
+        <v>8100</v>
       </c>
       <c r="N4" t="n">
-        <v>0.09</v>
+        <v>1.15</v>
       </c>
       <c r="O4" t="n">
-        <v>189497604790</v>
+        <v>59311516290</v>
       </c>
       <c r="P4" t="n">
-        <v>28800</v>
+        <v>9820</v>
       </c>
       <c r="Q4" t="n">
-        <v>11550</v>
+        <v>2965</v>
       </c>
       <c r="R4" t="n">
-        <v>-21000</v>
+        <v>-63000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>멜콘, 마이크론 반도체 장비 평가 완료 및 ASML 공급망 진입. AI 데이터센터 공급계약, 저평가된 시가총액 및 반도체 대장주로서의 전망.</t>
+          <t>샌즈랩, 미국 양자컴퓨터 및 보안주 강세와 국내 IT 보안 사고 뉴스에 따른 관심 증가. AI 시대 보안 중요성 부각.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['마이크론', 'AI', '공급계약']</t>
+          <t>['AI 보안', '양자컴퓨터', 'IT 보안']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>나무가</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19000</v>
+        <v>17690</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.18%</t>
+          <t>'+11.75%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.61</v>
+        <v>1.02</v>
       </c>
       <c r="E5" t="n">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="F5" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G5" t="n">
-        <v>278</v>
+        <v>232</v>
       </c>
       <c r="H5" t="n">
-        <v>4.74</v>
+        <v>1.11</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>17090</v>
+        <v>15830</v>
       </c>
       <c r="K5" t="n">
-        <v>19270</v>
+        <v>17170</v>
       </c>
       <c r="L5" t="n">
-        <v>20450</v>
+        <v>18530</v>
       </c>
       <c r="M5" t="n">
-        <v>18070</v>
+        <v>15830</v>
       </c>
       <c r="N5" t="n">
-        <v>4.13</v>
+        <v>0.09</v>
       </c>
       <c r="O5" t="n">
-        <v>37832691455</v>
+        <v>194877949665</v>
       </c>
       <c r="P5" t="n">
-        <v>28600</v>
+        <v>28800</v>
       </c>
       <c r="Q5" t="n">
-        <v>11050</v>
+        <v>11550</v>
       </c>
       <c r="R5" t="n">
-        <v>-34000</v>
+        <v>-21000</v>
       </c>
       <c r="S5" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>나무가, 아틀라스 휴머노이드 발주 및 로봇 부품 대장주로서의 입지 강화. 삼성, 구글, 현대차 등과의 협력 및 매년 300억대 이익 기대.</t>
+          <t>미국 마이크론 반도체 장비 평가 완료 및 ASML 공급망 진입 뉴스, AI 데이터센터 방열 시스템 594억 공급 계약, 삼성·SK·마이크론 등 글로벌 반도체 기업 납품 사실 등을 근거로 시가총액 3조 벨류, 적정가 4만 이상을 주장하며 긍정적인 전망을 제시합니다.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['휴머노이드', '로봇부품', '아틀라스']</t>
+          <t>['반도체 장비', '공급계약', '납품']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>190510</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>나무가</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15190</v>
+        <v>18900</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.88%</t>
+          <t>'+10.59%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.05</v>
+        <v>0.61</v>
       </c>
       <c r="E6" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G6" t="n">
-        <v>343</v>
+        <v>284</v>
       </c>
       <c r="H6" t="n">
-        <v>2.87</v>
+        <v>4.74</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>13700</v>
+        <v>17090</v>
       </c>
       <c r="K6" t="n">
-        <v>14210</v>
+        <v>19270</v>
       </c>
       <c r="L6" t="n">
-        <v>15290</v>
+        <v>20450</v>
       </c>
       <c r="M6" t="n">
-        <v>14210</v>
+        <v>18070</v>
       </c>
       <c r="N6" t="n">
-        <v>2.82</v>
+        <v>4.13</v>
       </c>
       <c r="O6" t="n">
-        <v>120046377105</v>
+        <v>38379602555</v>
       </c>
       <c r="P6" t="n">
-        <v>31500</v>
+        <v>28600</v>
       </c>
       <c r="Q6" t="n">
-        <v>1760</v>
+        <v>11050</v>
       </c>
       <c r="R6" t="n">
-        <v>247000</v>
+        <v>-34000</v>
       </c>
       <c r="S6" t="n">
-        <v>3000</v>
+        <v>9000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>대한광통신, 메타 유리 기판 및 해상광통신 케이블 관련 기대감. 외인 프로그램 매수세 유입 및 공매도 관련 언급.</t>
+          <t>아틀라스 1만대 발주, 미국 휴머노이드 폭등, 현대차 로봇 2만5000대 도입 등 로봇 관련 호재와 함께 나무가의 인공눈알 이식, 아틀라스 부품 대장으로서의 입지, 매년 300억대 이익 실현 등을 근거로 긍정적인 전망을 제시합니다.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['해상광통신', '유리기판', '외인매수']</t>
+          <t>['휴머노이드', '아틀라스', '로봇']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,130 +1016,130 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>190510</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>187200</v>
+        <v>15070</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.41%</t>
+          <t>'+10.00%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>63</v>
+        <v>111</v>
       </c>
       <c r="F7" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G7" t="n">
-        <v>218</v>
+        <v>379</v>
       </c>
       <c r="H7" t="n">
-        <v>74.90000000000001</v>
+        <v>2.87</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>171100</v>
+        <v>13700</v>
       </c>
       <c r="K7" t="n">
-        <v>176300</v>
+        <v>14210</v>
       </c>
       <c r="L7" t="n">
-        <v>189000</v>
+        <v>15290</v>
       </c>
       <c r="M7" t="n">
-        <v>175400</v>
+        <v>14210</v>
       </c>
       <c r="N7" t="n">
-        <v>74.89</v>
+        <v>2.82</v>
       </c>
       <c r="O7" t="n">
-        <v>475348126150</v>
+        <v>130293924675</v>
       </c>
       <c r="P7" t="n">
-        <v>243500</v>
+        <v>31500</v>
       </c>
       <c r="Q7" t="n">
-        <v>71000</v>
+        <v>1760</v>
       </c>
       <c r="R7" t="n">
-        <v>654000</v>
+        <v>247000</v>
       </c>
       <c r="S7" t="n">
-        <v>-1000</v>
+        <v>3000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>삼성전자우, 외국인 매수세 및 숏 스퀴즈 가능성 언급. 자사주 매입 기대.</t>
+          <t>메타 유리기판, 해상광통신 케이블 관련 기대감과 함께 루멘텀, 코히어런트 급등, 외인 프로그램 적극 매수 등을 근거로 2만 돌파 및 대세 상승을 전망하며, 공매도 세력을 언급하며 긍정적인 논조를 보입니다.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['숏 스퀴즈', '자사주매입', '우선주']</t>
+          <t>['해상광통신', '외인매수', '대세상승']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1447000</v>
+        <v>187900</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+7.90%</t>
+          <t>'+9.82%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>64</v>
       </c>
       <c r="F8" t="n">
-        <v>477</v>
+        <v>49</v>
       </c>
       <c r="G8" t="n">
-        <v>1836</v>
+        <v>223</v>
       </c>
       <c r="H8" t="n">
-        <v>48.61</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,60 +1147,60 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1341000</v>
+        <v>171100</v>
       </c>
       <c r="K8" t="n">
-        <v>1390000</v>
+        <v>176300</v>
       </c>
       <c r="L8" t="n">
-        <v>1467000</v>
+        <v>189000</v>
       </c>
       <c r="M8" t="n">
-        <v>1358000</v>
+        <v>175400</v>
       </c>
       <c r="N8" t="n">
-        <v>48.66</v>
+        <v>74.89</v>
       </c>
       <c r="O8" t="n">
-        <v>2947398166500</v>
+        <v>486202967700</v>
       </c>
       <c r="P8" t="n">
-        <v>2987000</v>
+        <v>243500</v>
       </c>
       <c r="Q8" t="n">
-        <v>501000</v>
+        <v>71000</v>
       </c>
       <c r="R8" t="n">
-        <v>53000</v>
+        <v>654000</v>
       </c>
       <c r="S8" t="n">
-        <v>55000</v>
+        <v>-1000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>SK하이닉스, 2029년까지 HBM 사실상 완판 전망 및 자사주 20조 취득. 긍정적인 컨퍼런스콜 내용과 주가 상승 기대감.</t>
+          <t>삼성전자우, 외국인 매수세 및 숏 스퀴즈 가능성 언급. 자사주 매입 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['HBM', '완판', '자사주']</t>
+          <t>['숏 스퀴즈', '자사주매입', '우선주']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>239500</v>
+        <v>240000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+7.88%</t>
+          <t>'+8.11%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="G9" t="n">
-        <v>1729</v>
+        <v>1777</v>
       </c>
       <c r="H9" t="n">
         <v>46.15</v>
@@ -1254,7 +1254,7 @@
         <v>46.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1899989386500</v>
+        <v>1991201987000</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>삼성전자, HBM4 점유율 경쟁 및 26만 전자 가능성 언급. 긍정적 시장 전망과 더불어 매수 추천 의견 존재.</t>
+          <t>이재명 대통령 관련 언급과 함께 HBM4 점유율 경쟁 및 피봇 후 반등 기대감을 보이며, 25일 매수 추천 및 26만 전자, 30만 전자 가능성을 제시합니다.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['HBM4', '점유율', '매수']</t>
+          <t>['HBM4', '점유율', '피봇']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,92 +1299,92 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8760</v>
+        <v>1447000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+6.83%</t>
+          <t>'+7.90%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.27</v>
+        <v>-0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>60</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>47</v>
+        <v>490</v>
       </c>
       <c r="G10" t="n">
-        <v>71</v>
+        <v>1798</v>
       </c>
       <c r="H10" t="n">
-        <v>1.42</v>
+        <v>48.61</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>8200</v>
+        <v>1341000</v>
       </c>
       <c r="K10" t="n">
-        <v>8230</v>
+        <v>1390000</v>
       </c>
       <c r="L10" t="n">
-        <v>9050</v>
+        <v>1467000</v>
       </c>
       <c r="M10" t="n">
-        <v>8100</v>
+        <v>1358000</v>
       </c>
       <c r="N10" t="n">
-        <v>1.15</v>
+        <v>48.66</v>
       </c>
       <c r="O10" t="n">
-        <v>48493999880</v>
+        <v>3031255938000</v>
       </c>
       <c r="P10" t="n">
-        <v>9820</v>
+        <v>2987000</v>
       </c>
       <c r="Q10" t="n">
-        <v>2965</v>
+        <v>501000</v>
       </c>
       <c r="R10" t="n">
-        <v>-63000</v>
+        <v>53000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>55000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>샌즈랩, 미국 양자컴퓨터 및 보안주 강세와 국내 IT 보안 사고 뉴스에 따른 관심 증가. AI 시대 보안 중요성 부각.</t>
+          <t>2029년까지 D램·HBM 사실상 완판, 20조 자사주 취득 발표, 컨퍼런스콜 성공적 마무리 등으로 업황 불신 해소 및 주가 상승 기대감이 높으며, 300만, 470만, 550만 등 목표가를 제시합니다.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['AI 보안', '양자컴퓨터', 'IT 보안']</t>
+          <t>['HBM', '완판', '자사주']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2615</v>
+        <v>2620</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+6.73%</t>
+          <t>'+6.94%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.68</v>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F11" t="n">
         <v>42</v>
       </c>
       <c r="G11" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H11" t="n">
         <v>1.69</v>
@@ -1438,7 +1438,7 @@
         <v>1.01</v>
       </c>
       <c r="O11" t="n">
-        <v>65198596019</v>
+        <v>66088035210</v>
       </c>
       <c r="P11" t="n">
         <v>2965</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>182800</v>
+        <v>182700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+4.88%</t>
+          <t>'+4.82%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="F12" t="n">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="G12" t="n">
-        <v>1398</v>
+        <v>1424</v>
       </c>
       <c r="H12" t="n">
         <v>35.43</v>
@@ -1530,7 +1530,7 @@
         <v>35.49</v>
       </c>
       <c r="O12" t="n">
-        <v>100011990100</v>
+        <v>102030696450</v>
       </c>
       <c r="P12" t="n">
         <v>304000</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>64000</v>
+        <v>64200</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.89%</t>
+          <t>'+3.22%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.57</v>
       </c>
       <c r="E13" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F13" t="n">
         <v>56</v>
       </c>
       <c r="G13" t="n">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="H13" t="n">
         <v>41.01</v>
@@ -1622,7 +1622,7 @@
         <v>40.44</v>
       </c>
       <c r="O13" t="n">
-        <v>139918003100</v>
+        <v>142819304250</v>
       </c>
       <c r="P13" t="n">
         <v>67300</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>삼성E&amp;A, 코스피 수익률 1위 달성 및 프로그램 매수세 유입. 추세 전환 가능성과 자사주 매입 기대감 표출.</t>
+          <t>최근 4일간 코스피 수익률 1위 달성, 자사주 매입 진행, 프로그램 매수세 유입 확인, 추세 전환점 유력시 등 긍정적인 분석과 함께 상승에 대한 기대감을 보입니다.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['수익률', '프로그램매수', '자사주매입']</t>
+          <t>['수익률', '자사주매입', '추세전환']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,21 +1671,21 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30350</v>
+        <v>30400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.88%</t>
+          <t>'+3.05%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F14" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G14" t="n">
         <v>255</v>
@@ -1714,7 +1714,7 @@
         <v>28.82</v>
       </c>
       <c r="O14" t="n">
-        <v>22314833900</v>
+        <v>22517673050</v>
       </c>
       <c r="P14" t="n">
         <v>69700</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2225</v>
+        <v>2220</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.53%</t>
+          <t>'+2.30%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.18</v>
       </c>
       <c r="E15" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F15" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G15" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H15" t="n">
         <v>5.07</v>
@@ -1806,7 +1806,7 @@
         <v>4.89</v>
       </c>
       <c r="O15" t="n">
-        <v>40384023525</v>
+        <v>40915010436</v>
       </c>
       <c r="P15" t="n">
         <v>4980</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16440</v>
+        <v>16420</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.31%</t>
+          <t>'+0.18%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F16" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G16" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="H16" t="n">
         <v>28.03</v>
@@ -1898,7 +1898,7 @@
         <v>27.96</v>
       </c>
       <c r="O16" t="n">
-        <v>28923162425</v>
+        <v>30033107460</v>
       </c>
       <c r="P16" t="n">
         <v>35350</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52100</v>
+        <v>52200</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.70%</t>
+          <t>'-1.51%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.03</v>
       </c>
       <c r="E17" t="n">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="F17" t="n">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G17" t="n">
-        <v>830</v>
+        <v>873</v>
       </c>
       <c r="H17" t="n">
         <v>10.31</v>
@@ -1990,7 +1990,7 @@
         <v>10.34</v>
       </c>
       <c r="O17" t="n">
-        <v>49161968250</v>
+        <v>50838040800</v>
       </c>
       <c r="P17" t="n">
         <v>154800</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>한화오션, 코스피 지수 상승에도 주가 하락 및 외국인 매도세. 자사주 매입 및 잠수함 관련 긍정적 뉴스에도 부정적 전망.</t>
+          <t>실적 발표 시 주가 하락, 외국인 폭격, 조선업보다는 한화 자체의 문제 제기, 대주주 매도 등으로 부정적인 전망이 나오지만, 미 해군 상륙함 건조 제안 등 일부 긍정적인 뉴스도 언급됩니다.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['잠수함', '외국인매도', '자사주매입']</t>
+          <t>['실적', '외국인', '건조제안']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14160</v>
+        <v>14200</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.01%</t>
+          <t>'-1.73%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="F18" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G18" t="n">
-        <v>297</v>
+        <v>316</v>
       </c>
       <c r="H18" t="n">
         <v>9.83</v>
@@ -2076,13 +2076,13 @@
         <v>14870</v>
       </c>
       <c r="M18" t="n">
-        <v>14140</v>
+        <v>14110</v>
       </c>
       <c r="N18" t="n">
         <v>10.02</v>
       </c>
       <c r="O18" t="n">
-        <v>38640343815</v>
+        <v>41210804975</v>
       </c>
       <c r="P18" t="n">
         <v>40350</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>대우건설, 주가조작 및 공매도 의혹 제기. 새 경영진에 대한 불만과 타 건설사 대비 부진한 주가 흐름 지적.</t>
+          <t>회사 연관 가능성 언급, 주가 조작 의혹 제기, SK하이닉스와의 주가 비교, 외인/기관 프로그램 매도 예상 등 부정적인 내용이 주를 이루며, 회사의 변화와 성과를 촉구합니다.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가조작', '공매도', '대차']</t>
+          <t>['주가조작', '외인매도', '프로그램']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2005</v>
+        <v>1992</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.84%</t>
+          <t>'-4.46%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.39</v>
       </c>
       <c r="E19" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F19" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G19" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H19" t="n">
         <v>2.52</v>
@@ -2174,7 +2174,7 @@
         <v>2.13</v>
       </c>
       <c r="O19" t="n">
-        <v>12725517317</v>
+        <v>13113149755</v>
       </c>
       <c r="P19" t="n">
         <v>6190</v>

--- a/data/trending_integrated_20261028_11.xlsx
+++ b/data/trending_integrated_20261028_11.xlsx
@@ -578,13 +578,13 @@
         <v>-0.19</v>
       </c>
       <c r="E2" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F2" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G2" t="n">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -610,7 +610,7 @@
         <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>147732832776</v>
+        <v>148157912126</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등, 27일 애프터 종가 3470원 돌파, 갭 15% 상승 등 긍정적인 신호와 함께 상한가 기대감을 보이며, 과거 쓰레기 회사라는 인식에서 벗어나 호재와 미장 상승을 바탕으로 급등 가능성을 제시합니다.</t>
+          <t>빛과전자, 미국 광통신주 급등에 따른 동반 상승 기대. 2분기 실적 발표 후 매물대 돌파 및 상한가 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광통신', '상승', '호재']</t>
+          <t>['광통신', '실적발표', '상한가']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28800</v>
+        <v>28950</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+21.26%</t>
+          <t>'+21.89%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F3" t="n">
         <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="H3" t="n">
         <v>5.16</v>
@@ -702,7 +702,7 @@
         <v>5.31</v>
       </c>
       <c r="O3" t="n">
-        <v>135922791700</v>
+        <v>138816156725</v>
       </c>
       <c r="P3" t="n">
         <v>50600</v>
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9180</v>
+        <v>17490</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+11.95%</t>
+          <t>'+10.49%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.27</v>
+        <v>1.02</v>
       </c>
       <c r="E4" t="n">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="F4" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="G4" t="n">
-        <v>81</v>
+        <v>238</v>
       </c>
       <c r="H4" t="n">
-        <v>1.42</v>
+        <v>1.11</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,91 +779,91 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>8200</v>
+        <v>15830</v>
       </c>
       <c r="K4" t="n">
-        <v>8230</v>
+        <v>17170</v>
       </c>
       <c r="L4" t="n">
-        <v>9190</v>
+        <v>18530</v>
       </c>
       <c r="M4" t="n">
-        <v>8100</v>
+        <v>15830</v>
       </c>
       <c r="N4" t="n">
-        <v>1.15</v>
+        <v>0.09</v>
       </c>
       <c r="O4" t="n">
-        <v>59311516290</v>
+        <v>198692172130</v>
       </c>
       <c r="P4" t="n">
-        <v>9820</v>
+        <v>28800</v>
       </c>
       <c r="Q4" t="n">
-        <v>2965</v>
+        <v>11550</v>
       </c>
       <c r="R4" t="n">
-        <v>-63000</v>
+        <v>-21000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>샌즈랩, 미국 양자컴퓨터 및 보안주 강세와 국내 IT 보안 사고 뉴스에 따른 관심 증가. AI 시대 보안 중요성 부각.</t>
+          <t>멜콘, 마이크론 반도체 장비 평가 완료 및 ASML 공급망 진입 뉴스. AI 데이터센터 방열 시스템 공급 계약 체결 등 호재 반영.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['AI 보안', '양자컴퓨터', 'IT 보안']</t>
+          <t>['반도체장비', '공급계약', '밸류에이션']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17690</v>
+        <v>15110</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.75%</t>
+          <t>'+10.29%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.02</v>
+        <v>0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="F5" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="G5" t="n">
-        <v>232</v>
+        <v>395</v>
       </c>
       <c r="H5" t="n">
-        <v>1.11</v>
+        <v>2.87</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>15830</v>
+        <v>13700</v>
       </c>
       <c r="K5" t="n">
-        <v>17170</v>
+        <v>14210</v>
       </c>
       <c r="L5" t="n">
-        <v>18530</v>
+        <v>15290</v>
       </c>
       <c r="M5" t="n">
-        <v>15830</v>
+        <v>14210</v>
       </c>
       <c r="N5" t="n">
-        <v>0.09</v>
+        <v>2.82</v>
       </c>
       <c r="O5" t="n">
-        <v>194877949665</v>
+        <v>136696211155</v>
       </c>
       <c r="P5" t="n">
-        <v>28800</v>
+        <v>31500</v>
       </c>
       <c r="Q5" t="n">
-        <v>11550</v>
+        <v>1760</v>
       </c>
       <c r="R5" t="n">
-        <v>-21000</v>
+        <v>247000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 마이크론 반도체 장비 평가 완료 및 ASML 공급망 진입 뉴스, AI 데이터센터 방열 시스템 594억 공급 계약, 삼성·SK·마이크론 등 글로벌 반도체 기업 납품 사실 등을 근거로 시가총액 3조 벨류, 적정가 4만 이상을 주장하며 긍정적인 전망을 제시합니다.</t>
+          <t>대한광통신, 메타 해상광통신 케이블 관련주로 부각. 외인 프로그램 매수세 유입 및 공매도 세력에 대한 경고.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0.45</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체 장비', '공급계약', '납품']</t>
+          <t>['해상광통신', '케이블', '외국인매수']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18900</v>
+        <v>18810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.59%</t>
+          <t>'+10.06%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.61</v>
       </c>
       <c r="E6" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F6" t="n">
         <v>61</v>
       </c>
       <c r="G6" t="n">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="H6" t="n">
         <v>4.74</v>
@@ -978,7 +978,7 @@
         <v>4.13</v>
       </c>
       <c r="O6" t="n">
-        <v>38379602555</v>
+        <v>38856891465</v>
       </c>
       <c r="P6" t="n">
         <v>28600</v>
@@ -1023,162 +1023,162 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15070</v>
+        <v>187600</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+10.00%</t>
+          <t>'+9.64%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="F7" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G7" t="n">
-        <v>379</v>
+        <v>234</v>
       </c>
       <c r="H7" t="n">
-        <v>2.87</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>13700</v>
+        <v>171100</v>
       </c>
       <c r="K7" t="n">
-        <v>14210</v>
+        <v>176300</v>
       </c>
       <c r="L7" t="n">
-        <v>15290</v>
+        <v>189000</v>
       </c>
       <c r="M7" t="n">
-        <v>14210</v>
+        <v>175400</v>
       </c>
       <c r="N7" t="n">
-        <v>2.82</v>
+        <v>74.89</v>
       </c>
       <c r="O7" t="n">
-        <v>130293924675</v>
+        <v>498351659950</v>
       </c>
       <c r="P7" t="n">
-        <v>31500</v>
+        <v>243500</v>
       </c>
       <c r="Q7" t="n">
-        <v>1760</v>
+        <v>71000</v>
       </c>
       <c r="R7" t="n">
-        <v>247000</v>
+        <v>654000</v>
       </c>
       <c r="S7" t="n">
-        <v>3000</v>
+        <v>-1000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>메타 유리기판, 해상광통신 케이블 관련 기대감과 함께 루멘텀, 코히어런트 급등, 외인 프로그램 적극 매수 등을 근거로 2만 돌파 및 대세 상승을 전망하며, 공매도 세력을 언급하며 긍정적인 논조를 보입니다.</t>
+          <t>삼성전자우, 외국인 매수세 및 숏 스퀴즈 가능성 언급. 자사주 매입 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['해상광통신', '외인매수', '대세상승']</t>
+          <t>['숏 스퀴즈', '자사주매입', '우선주']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>187900</v>
+        <v>8970</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+9.82%</t>
+          <t>'+9.39%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.01</v>
+        <v>0.27</v>
       </c>
       <c r="E8" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="F8" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="G8" t="n">
-        <v>223</v>
+        <v>81</v>
       </c>
       <c r="H8" t="n">
-        <v>74.90000000000001</v>
+        <v>1.42</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>171100</v>
+        <v>8200</v>
       </c>
       <c r="K8" t="n">
-        <v>176300</v>
+        <v>8230</v>
       </c>
       <c r="L8" t="n">
-        <v>189000</v>
+        <v>9220</v>
       </c>
       <c r="M8" t="n">
-        <v>175400</v>
+        <v>8100</v>
       </c>
       <c r="N8" t="n">
-        <v>74.89</v>
+        <v>1.15</v>
       </c>
       <c r="O8" t="n">
-        <v>486202967700</v>
+        <v>66525503845</v>
       </c>
       <c r="P8" t="n">
-        <v>243500</v>
+        <v>9820</v>
       </c>
       <c r="Q8" t="n">
-        <v>71000</v>
+        <v>2965</v>
       </c>
       <c r="R8" t="n">
-        <v>654000</v>
+        <v>-63000</v>
       </c>
       <c r="S8" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>삼성전자우, 외국인 매수세 및 숏 스퀴즈 가능성 언급. 자사주 매입 기대.</t>
+          <t>샌즈랩, 미국 양자컴퓨터 및 보안주 강세와 국내 IT 보안 사고 뉴스에 따른 관심 증가. AI 시대 보안 중요성 부각.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['숏 스퀴즈', '자사주매입', '우선주']</t>
+          <t>['AI 보안', '양자컴퓨터', 'IT 보안']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>240000</v>
+        <v>1448000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.11%</t>
+          <t>'+7.98%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E9" t="n">
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="G9" t="n">
-        <v>1777</v>
+        <v>1806</v>
       </c>
       <c r="H9" t="n">
-        <v>46.15</v>
+        <v>48.61</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,47 +1239,47 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>222000</v>
+        <v>1341000</v>
       </c>
       <c r="K9" t="n">
-        <v>231000</v>
+        <v>1390000</v>
       </c>
       <c r="L9" t="n">
-        <v>243000</v>
+        <v>1467000</v>
       </c>
       <c r="M9" t="n">
-        <v>228000</v>
+        <v>1358000</v>
       </c>
       <c r="N9" t="n">
-        <v>46.1</v>
+        <v>48.66</v>
       </c>
       <c r="O9" t="n">
-        <v>1991201987000</v>
+        <v>3097893310000</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>94500</v>
+        <v>501000</v>
       </c>
       <c r="R9" t="n">
-        <v>1304000</v>
+        <v>53000</v>
       </c>
       <c r="S9" t="n">
-        <v>524000</v>
+        <v>55000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>이재명 대통령 관련 언급과 함께 HBM4 점유율 경쟁 및 피봇 후 반등 기대감을 보이며, 25일 매수 추천 및 26만 전자, 30만 전자 가능성을 제시합니다.</t>
+          <t>SK하이닉스 2029년까지 HBM 사실상 완판 전망 및 20조 자사주 매입 발표. 컨퍼런스콜 성공적 마무리 및 목표가 상향 제시.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['HBM4', '점유율', '피봇']</t>
+          <t>['HBM', '완판', '자사주매입']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1447000</v>
+        <v>239000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+7.90%</t>
+          <t>'+7.66%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="E10" t="n">
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="G10" t="n">
-        <v>1798</v>
+        <v>1821</v>
       </c>
       <c r="H10" t="n">
-        <v>48.61</v>
+        <v>46.15</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,47 +1331,47 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1341000</v>
+        <v>222000</v>
       </c>
       <c r="K10" t="n">
-        <v>1390000</v>
+        <v>231000</v>
       </c>
       <c r="L10" t="n">
-        <v>1467000</v>
+        <v>243000</v>
       </c>
       <c r="M10" t="n">
-        <v>1358000</v>
+        <v>228000</v>
       </c>
       <c r="N10" t="n">
-        <v>48.66</v>
+        <v>46.1</v>
       </c>
       <c r="O10" t="n">
-        <v>3031255938000</v>
+        <v>2060545194250</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>501000</v>
+        <v>94500</v>
       </c>
       <c r="R10" t="n">
-        <v>53000</v>
+        <v>1304000</v>
       </c>
       <c r="S10" t="n">
-        <v>55000</v>
+        <v>524000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2029년까지 D램·HBM 사실상 완판, 20조 자사주 취득 발표, 컨퍼런스콜 성공적 마무리 등으로 업황 불신 해소 및 주가 상승 기대감이 높으며, 300만, 470만, 550만 등 목표가를 제시합니다.</t>
+          <t>삼성전자 HBM4 점유율 경쟁 및 26만/30만 전자 목표 제시. 해외 시장 및 국내 유가 안정 관련 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['HBM', '완판', '자사주']</t>
+          <t>['HBM4', '점유율', '목표가']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2620</v>
+        <v>2605</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+6.94%</t>
+          <t>'+6.33%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.68</v>
       </c>
       <c r="E11" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="F11" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G11" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H11" t="n">
         <v>1.69</v>
@@ -1438,7 +1438,7 @@
         <v>1.01</v>
       </c>
       <c r="O11" t="n">
-        <v>66088035210</v>
+        <v>67149682150</v>
       </c>
       <c r="P11" t="n">
         <v>2965</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>182700</v>
+        <v>182400</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+4.82%</t>
+          <t>'+4.65%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="F12" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="G12" t="n">
-        <v>1424</v>
+        <v>1504</v>
       </c>
       <c r="H12" t="n">
         <v>35.43</v>
@@ -1530,7 +1530,7 @@
         <v>35.49</v>
       </c>
       <c r="O12" t="n">
-        <v>102030696450</v>
+        <v>103763613150</v>
       </c>
       <c r="P12" t="n">
         <v>304000</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>엔비디아의 주요 주주 등극 가능성에 대한 언급과 함께 주가 상승 기대감 표출. 다만, 연기금 매도 및 과거 삼성전자/SK하이닉스와의 비교를 통해 신중론도 제기.</t>
+          <t>NAVER, 주가 부진 및 공매도 비율 증가에 대한 불만 제기. 지수 대비 낮은 상승률 및 소외주로 분류되는 상황 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.05</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['엔비디아', '주주', '신중론']</t>
+          <t>['공매도', '주가부진', '소외주']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>64200</v>
+        <v>30400</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.22%</t>
+          <t>'+3.05%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.57</v>
+        <v>-0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F13" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="G13" t="n">
-        <v>422</v>
+        <v>298</v>
       </c>
       <c r="H13" t="n">
-        <v>41.01</v>
+        <v>28.81</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>62200</v>
+        <v>29500</v>
       </c>
       <c r="K13" t="n">
-        <v>63000</v>
+        <v>29900</v>
       </c>
       <c r="L13" t="n">
-        <v>64500</v>
+        <v>30650</v>
       </c>
       <c r="M13" t="n">
-        <v>62200</v>
+        <v>29900</v>
       </c>
       <c r="N13" t="n">
-        <v>40.44</v>
+        <v>28.82</v>
       </c>
       <c r="O13" t="n">
-        <v>142819304250</v>
+        <v>22916263375</v>
       </c>
       <c r="P13" t="n">
-        <v>67300</v>
+        <v>69700</v>
       </c>
       <c r="Q13" t="n">
-        <v>23150</v>
+        <v>29200</v>
       </c>
       <c r="R13" t="n">
-        <v>337000</v>
+        <v>120000</v>
       </c>
       <c r="S13" t="n">
-        <v>18000</v>
+        <v>14000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>최근 4일간 코스피 수익률 1위 달성, 자사주 매입 진행, 프로그램 매수세 유입 확인, 추세 전환점 유력시 등 긍정적인 분석과 함께 상승에 대한 기대감을 보입니다.</t>
+          <t>종목에 대한 부정적 감정 표출 및 불확실한 하락 전망. 네이버 대비 경쟁력 약화 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['수익률', '자사주매입', '추세전환']</t>
+          <t>['공매도', '거래량', '적정주가']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>035720</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30400</v>
+        <v>64000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+3.05%</t>
+          <t>'+2.89%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.01</v>
+        <v>0.57</v>
       </c>
       <c r="E14" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F14" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="G14" t="n">
-        <v>255</v>
+        <v>463</v>
       </c>
       <c r="H14" t="n">
-        <v>28.81</v>
+        <v>41.01</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,60 +1699,60 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>29500</v>
+        <v>62200</v>
       </c>
       <c r="K14" t="n">
-        <v>29900</v>
+        <v>63000</v>
       </c>
       <c r="L14" t="n">
-        <v>30650</v>
+        <v>64500</v>
       </c>
       <c r="M14" t="n">
-        <v>29900</v>
+        <v>62200</v>
       </c>
       <c r="N14" t="n">
-        <v>28.82</v>
+        <v>40.44</v>
       </c>
       <c r="O14" t="n">
-        <v>22517673050</v>
+        <v>146006083100</v>
       </c>
       <c r="P14" t="n">
-        <v>69700</v>
+        <v>67300</v>
       </c>
       <c r="Q14" t="n">
-        <v>29200</v>
+        <v>23150</v>
       </c>
       <c r="R14" t="n">
-        <v>120000</v>
+        <v>337000</v>
       </c>
       <c r="S14" t="n">
-        <v>14000</v>
+        <v>18000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>카카오, 주가 하락세 지속 및 낮은 적정 가치에 대한 부정적 의견. 거래량 부진 시 추가 하락 가능성 언급.</t>
+          <t>삼성E&amp;A 코스피 수익률 1위 달성 및 자사주 매입 지속. 공매도 세력에 대한 경고와 함께 추세 전환 전망 제시.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['적정주가', '하락세', '거래량']</t>
+          <t>['자사주매입', '수익률', '추세전환']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>035720</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2220</v>
+        <v>2215</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.30%</t>
+          <t>'+2.07%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.18</v>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G15" t="n">
-        <v>168</v>
+        <v>205</v>
       </c>
       <c r="H15" t="n">
         <v>5.07</v>
@@ -1806,7 +1806,7 @@
         <v>4.89</v>
       </c>
       <c r="O15" t="n">
-        <v>40915010436</v>
+        <v>42604376063</v>
       </c>
       <c r="P15" t="n">
         <v>4980</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16420</v>
+        <v>16390</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.18%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F16" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G16" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="H16" t="n">
         <v>28.03</v>
@@ -1898,7 +1898,7 @@
         <v>27.96</v>
       </c>
       <c r="O16" t="n">
-        <v>30033107460</v>
+        <v>30889760805</v>
       </c>
       <c r="P16" t="n">
         <v>35350</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52200</v>
+        <v>52100</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.51%</t>
+          <t>'-1.70%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.03</v>
       </c>
       <c r="E17" t="n">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="F17" t="n">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="G17" t="n">
-        <v>873</v>
+        <v>900</v>
       </c>
       <c r="H17" t="n">
         <v>10.31</v>
@@ -1990,7 +1990,7 @@
         <v>10.34</v>
       </c>
       <c r="O17" t="n">
-        <v>50838040800</v>
+        <v>53182042350</v>
       </c>
       <c r="P17" t="n">
         <v>154800</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>실적 발표 시 주가 하락, 외국인 폭격, 조선업보다는 한화 자체의 문제 제기, 대주주 매도 등으로 부정적인 전망이 나오지만, 미 해군 상륙함 건조 제안 등 일부 긍정적인 뉴스도 언급됩니다.</t>
+          <t>한화오션, 코스피 지수 상승에도 불구하고 주가 하락. 외국인 매도세 및 공매도에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['실적', '외국인', '건조제안']</t>
+          <t>['주가하락', '외국인매도', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14200</v>
+        <v>14180</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-1.73%</t>
+          <t>'-1.87%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="F18" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G18" t="n">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="H18" t="n">
         <v>9.83</v>
@@ -2082,7 +2082,7 @@
         <v>10.02</v>
       </c>
       <c r="O18" t="n">
-        <v>41210804975</v>
+        <v>42178223455</v>
       </c>
       <c r="P18" t="n">
         <v>40350</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>회사 연관 가능성 언급, 주가 조작 의혹 제기, SK하이닉스와의 주가 비교, 외인/기관 프로그램 매도 예상 등 부정적인 내용이 주를 이루며, 회사의 변화와 성과를 촉구합니다.</t>
+          <t>대우건설 주가 조작 및 공매도 관련 강한 비판. 새 경영진에 대한 불신 및 주가 부진에 대한 불만 토로.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가조작', '외인매도', '프로그램']</t>
+          <t>['주가조작', '공매도', '경영진']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,21 +2131,21 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1992</v>
+        <v>1997</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-4.46%</t>
+          <t>'-4.22%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.39</v>
       </c>
       <c r="E19" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F19" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G19" t="n">
         <v>100</v>
@@ -2174,7 +2174,7 @@
         <v>2.13</v>
       </c>
       <c r="O19" t="n">
-        <v>13113149755</v>
+        <v>13236241961</v>
       </c>
       <c r="P19" t="n">
         <v>6190</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>SK증권, 액면병합 가격 관련 문의 및 주가 하락에 대한 불만.</t>
+          <t>SK하이닉스 자사주 매입 공동 중개 호재에도 주가 하락. 액면병합 및 공매도 관련 우려 제기.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['액면병합', '공매', '전망']</t>
+          <t>['자사주매입', '공매도', '액면병합']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">

--- a/data/trending_integrated_20261028_11.xlsx
+++ b/data/trending_integrated_20261028_11.xlsx
@@ -578,7 +578,7 @@
         <v>-0.19</v>
       </c>
       <c r="E2" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F2" t="n">
         <v>75</v>
@@ -610,7 +610,7 @@
         <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>148157912126</v>
+        <v>148610426776</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>빛과전자, 미국 광통신주 급등에 따른 동반 상승 기대. 2분기 실적 발표 후 매물대 돌파 및 상한가 가능성 언급.</t>
+          <t>미국 광통신주 급등에 따른 기대감 형성. 긍정적 차트 패턴 및 급등 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광통신', '실적발표', '상한가']</t>
+          <t>['광통신', '차트', '급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28950</v>
+        <v>29100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+21.89%</t>
+          <t>'+22.53%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G3" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="H3" t="n">
         <v>5.16</v>
@@ -702,7 +702,7 @@
         <v>5.31</v>
       </c>
       <c r="O3" t="n">
-        <v>138816156725</v>
+        <v>140333045850</v>
       </c>
       <c r="P3" t="n">
         <v>50600</v>
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17490</v>
+        <v>9260</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+10.49%</t>
+          <t>'+12.93%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.02</v>
+        <v>0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="F4" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>238</v>
+        <v>74</v>
       </c>
       <c r="H4" t="n">
-        <v>1.11</v>
+        <v>1.42</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,91 +779,91 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>15830</v>
+        <v>8200</v>
       </c>
       <c r="K4" t="n">
-        <v>17170</v>
+        <v>8230</v>
       </c>
       <c r="L4" t="n">
-        <v>18530</v>
+        <v>9290</v>
       </c>
       <c r="M4" t="n">
-        <v>15830</v>
+        <v>8100</v>
       </c>
       <c r="N4" t="n">
-        <v>0.09</v>
+        <v>1.15</v>
       </c>
       <c r="O4" t="n">
-        <v>198692172130</v>
+        <v>75490453450</v>
       </c>
       <c r="P4" t="n">
-        <v>28800</v>
+        <v>9820</v>
       </c>
       <c r="Q4" t="n">
-        <v>11550</v>
+        <v>2965</v>
       </c>
       <c r="R4" t="n">
-        <v>-21000</v>
+        <v>-63000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>멜콘, 마이크론 반도체 장비 평가 완료 및 ASML 공급망 진입 뉴스. AI 데이터센터 방열 시스템 공급 계약 체결 등 호재 반영.</t>
+          <t>샌즈랩, 미국 양자컴퓨터 및 보안주 강세와 국내 IT 보안 사고 뉴스에 따른 관심 증가. AI 시대 보안 중요성 부각.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['반도체장비', '공급계약', '밸류에이션']</t>
+          <t>['AI 보안', '양자컴퓨터', 'IT 보안']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15110</v>
+        <v>17580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.29%</t>
+          <t>'+11.05%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.05</v>
+        <v>1.02</v>
       </c>
       <c r="E5" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F5" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="G5" t="n">
-        <v>395</v>
+        <v>227</v>
       </c>
       <c r="H5" t="n">
-        <v>2.87</v>
+        <v>1.11</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>13700</v>
+        <v>15830</v>
       </c>
       <c r="K5" t="n">
-        <v>14210</v>
+        <v>17170</v>
       </c>
       <c r="L5" t="n">
-        <v>15290</v>
+        <v>18530</v>
       </c>
       <c r="M5" t="n">
-        <v>14210</v>
+        <v>15830</v>
       </c>
       <c r="N5" t="n">
-        <v>2.82</v>
+        <v>0.09</v>
       </c>
       <c r="O5" t="n">
-        <v>136696211155</v>
+        <v>204744956620</v>
       </c>
       <c r="P5" t="n">
-        <v>31500</v>
+        <v>28800</v>
       </c>
       <c r="Q5" t="n">
-        <v>1760</v>
+        <v>11550</v>
       </c>
       <c r="R5" t="n">
-        <v>247000</v>
+        <v>-21000</v>
       </c>
       <c r="S5" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>대한광통신, 메타 해상광통신 케이블 관련주로 부각. 외인 프로그램 매수세 유입 및 공매도 세력에 대한 경고.</t>
+          <t>AI 데이터센터 방열 시스템 공급 계약 및 마이크론 반도체 장비 평가 완료. 밸류에이션 재평가 및 주가 급등 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['해상광통신', '케이블', '외국인매수']</t>
+          <t>['AI', '방열 시스템', '반도체 장비']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,222 +924,222 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>나무가</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18810</v>
+        <v>187300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.06%</t>
+          <t>'+9.47%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.61</v>
+        <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>110</v>
+        <v>64</v>
       </c>
       <c r="F6" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="G6" t="n">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="H6" t="n">
-        <v>4.74</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>17090</v>
+        <v>171100</v>
       </c>
       <c r="K6" t="n">
-        <v>19270</v>
+        <v>176300</v>
       </c>
       <c r="L6" t="n">
-        <v>20450</v>
+        <v>189000</v>
       </c>
       <c r="M6" t="n">
-        <v>18070</v>
+        <v>175400</v>
       </c>
       <c r="N6" t="n">
-        <v>4.13</v>
+        <v>74.89</v>
       </c>
       <c r="O6" t="n">
-        <v>38856891465</v>
+        <v>509577638150</v>
       </c>
       <c r="P6" t="n">
-        <v>28600</v>
+        <v>243500</v>
       </c>
       <c r="Q6" t="n">
-        <v>11050</v>
+        <v>71000</v>
       </c>
       <c r="R6" t="n">
-        <v>-34000</v>
+        <v>654000</v>
       </c>
       <c r="S6" t="n">
-        <v>9000</v>
+        <v>-1000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>아틀라스 1만대 발주, 미국 휴머노이드 폭등, 현대차 로봇 2만5000대 도입 등 로봇 관련 호재와 함께 나무가의 인공눈알 이식, 아틀라스 부품 대장으로서의 입지, 매년 300억대 이익 실현 등을 근거로 긍정적인 전망을 제시합니다.</t>
+          <t>삼성전자우, 외국인 매수세 및 숏 스퀴즈 가능성 언급. 자사주 매입 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['휴머노이드', '아틀라스', '로봇']</t>
+          <t>['숏 스퀴즈', '자사주매입', '우선주']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>190510</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>나무가</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>187600</v>
+        <v>18600</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.64%</t>
+          <t>'+8.84%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.01</v>
+        <v>0.61</v>
       </c>
       <c r="E7" t="n">
+        <v>116</v>
+      </c>
+      <c r="F7" t="n">
         <v>64</v>
       </c>
-      <c r="F7" t="n">
-        <v>49</v>
-      </c>
       <c r="G7" t="n">
-        <v>234</v>
+        <v>308</v>
       </c>
       <c r="H7" t="n">
-        <v>74.90000000000001</v>
+        <v>4.74</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>171100</v>
+        <v>17090</v>
       </c>
       <c r="K7" t="n">
-        <v>176300</v>
+        <v>19270</v>
       </c>
       <c r="L7" t="n">
-        <v>189000</v>
+        <v>20450</v>
       </c>
       <c r="M7" t="n">
-        <v>175400</v>
+        <v>18070</v>
       </c>
       <c r="N7" t="n">
-        <v>74.89</v>
+        <v>4.13</v>
       </c>
       <c r="O7" t="n">
-        <v>498351659950</v>
+        <v>39629446480</v>
       </c>
       <c r="P7" t="n">
-        <v>243500</v>
+        <v>28600</v>
       </c>
       <c r="Q7" t="n">
-        <v>71000</v>
+        <v>11050</v>
       </c>
       <c r="R7" t="n">
-        <v>654000</v>
+        <v>-34000</v>
       </c>
       <c r="S7" t="n">
-        <v>-1000</v>
+        <v>9000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>삼성전자우, 외국인 매수세 및 숏 스퀴즈 가능성 언급. 자사주 매입 기대.</t>
+          <t>아틀라스 휴머노이드 발주 및 로봇 사업 확장 기대. 카메라 모듈 공급 및 높은 이익률 기반 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['숏 스퀴즈', '자사주매입', '우선주']</t>
+          <t>['휴머노이드', '로봇', '카메라 모듈']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>190510</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8970</v>
+        <v>14880</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+9.39%</t>
+          <t>'+8.61%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.27</v>
+        <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="F8" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G8" t="n">
-        <v>81</v>
+        <v>416</v>
       </c>
       <c r="H8" t="n">
-        <v>1.42</v>
+        <v>2.87</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,60 +1147,60 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>8200</v>
+        <v>13700</v>
       </c>
       <c r="K8" t="n">
-        <v>8230</v>
+        <v>14210</v>
       </c>
       <c r="L8" t="n">
-        <v>9220</v>
+        <v>15290</v>
       </c>
       <c r="M8" t="n">
-        <v>8100</v>
+        <v>14210</v>
       </c>
       <c r="N8" t="n">
-        <v>1.15</v>
+        <v>2.82</v>
       </c>
       <c r="O8" t="n">
-        <v>66525503845</v>
+        <v>141217623325</v>
       </c>
       <c r="P8" t="n">
-        <v>9820</v>
+        <v>31500</v>
       </c>
       <c r="Q8" t="n">
-        <v>2965</v>
+        <v>1760</v>
       </c>
       <c r="R8" t="n">
-        <v>-63000</v>
+        <v>247000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>샌즈랩, 미국 양자컴퓨터 및 보안주 강세와 국내 IT 보안 사고 뉴스에 따른 관심 증가. AI 시대 보안 중요성 부각.</t>
+          <t>메타 유리 기판 및 해상 광통신 케이블 사업 기대감. 외국인 프로그램 매수세 유입 및 공매도 세력 압박.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['AI 보안', '양자컴퓨터', 'IT 보안']</t>
+          <t>['유리 기판', '광통신', '외국인 매수']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1448000</v>
+        <v>1452000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+7.98%</t>
+          <t>'+8.28%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="G9" t="n">
-        <v>1806</v>
+        <v>1837</v>
       </c>
       <c r="H9" t="n">
         <v>48.61</v>
@@ -1254,7 +1254,7 @@
         <v>48.66</v>
       </c>
       <c r="O9" t="n">
-        <v>3097893310000</v>
+        <v>3156467447500</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>SK하이닉스 2029년까지 HBM 사실상 완판 전망 및 20조 자사주 매입 발표. 컨퍼런스콜 성공적 마무리 및 목표가 상향 제시.</t>
+          <t>29년까지 HBM 완판 전망 및 자사주 20조 취득 발표. 반도체 업황 호조에 따른 주가 상승 기대감 고조.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['HBM', '완판', '자사주매입']</t>
+          <t>['HBM', '자사주 매입', '반도체 업황']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>239000</v>
+        <v>239500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+7.66%</t>
+          <t>'+7.88%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,7 +1317,7 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G10" t="n">
         <v>1821</v>
@@ -1346,7 +1346,7 @@
         <v>46.1</v>
       </c>
       <c r="O10" t="n">
-        <v>2060545194250</v>
+        <v>2097307612750</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>삼성전자 HBM4 점유율 경쟁 및 26만/30만 전자 목표 제시. 해외 시장 및 국내 유가 안정 관련 언급.</t>
+          <t>AI HBM4 점유율 경쟁 및 반도체 업황 호조 전망. 시장 참여자들의 긍정적 기대감 형성.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['HBM4', '점유율', '목표가']</t>
+          <t>['HBM4', 'AI', '반도체']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2605</v>
+        <v>2600</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+6.33%</t>
+          <t>'+6.12%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.68</v>
       </c>
       <c r="E11" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F11" t="n">
         <v>46</v>
       </c>
       <c r="G11" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H11" t="n">
         <v>1.69</v>
@@ -1438,7 +1438,7 @@
         <v>1.01</v>
       </c>
       <c r="O11" t="n">
-        <v>67149682150</v>
+        <v>69318369462</v>
       </c>
       <c r="P11" t="n">
         <v>2965</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈, 미국 1000억원 규모 하이브리드 부품 수주 및 개인 물량 흡수 후 상승 기대.</t>
+          <t>개인 물량 흡수 및 거래량 증가. 주가 상승 전환 가능성 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['수주', '하이브리드', '부품']</t>
+          <t>['개인 물량', '거래량', '주가 상승']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>182400</v>
+        <v>182200</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+4.65%</t>
+          <t>'+4.53%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="F12" t="n">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="G12" t="n">
-        <v>1504</v>
+        <v>1497</v>
       </c>
       <c r="H12" t="n">
         <v>35.43</v>
@@ -1530,7 +1530,7 @@
         <v>35.49</v>
       </c>
       <c r="O12" t="n">
-        <v>103763613150</v>
+        <v>106299580300</v>
       </c>
       <c r="P12" t="n">
         <v>304000</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>NAVER, 주가 부진 및 공매도 비율 증가에 대한 불만 제기. 지수 대비 낮은 상승률 및 소외주로 분류되는 상황 언급.</t>
+          <t>프로그램 매수세와 야간 선물 상승에도 불구하고, 공매도 비율에 대한 우려와 기대감 없는 3행시가 제시됨. 외인 비중은 소폭 하락.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['공매도', '주가부진', '소외주']</t>
+          <t>['공매도', '프로그램 매수', '야간 선물']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,11 +1575,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30400</v>
+        <v>64100</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1587,19 +1587,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.01</v>
+        <v>0.57</v>
       </c>
       <c r="E13" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F13" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G13" t="n">
-        <v>298</v>
+        <v>473</v>
       </c>
       <c r="H13" t="n">
-        <v>28.81</v>
+        <v>41.01</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>29500</v>
+        <v>62200</v>
       </c>
       <c r="K13" t="n">
-        <v>29900</v>
+        <v>63000</v>
       </c>
       <c r="L13" t="n">
-        <v>30650</v>
+        <v>64500</v>
       </c>
       <c r="M13" t="n">
-        <v>29900</v>
+        <v>62200</v>
       </c>
       <c r="N13" t="n">
-        <v>28.82</v>
+        <v>40.44</v>
       </c>
       <c r="O13" t="n">
-        <v>22916263375</v>
+        <v>150949424800</v>
       </c>
       <c r="P13" t="n">
-        <v>69700</v>
+        <v>67300</v>
       </c>
       <c r="Q13" t="n">
-        <v>29200</v>
+        <v>23150</v>
       </c>
       <c r="R13" t="n">
-        <v>120000</v>
+        <v>337000</v>
       </c>
       <c r="S13" t="n">
-        <v>14000</v>
+        <v>18000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>종목에 대한 부정적 감정 표출 및 불확실한 하락 전망. 네이버 대비 경쟁력 약화 언급.</t>
+          <t>자사주 매입 지속 및 코스피 수익률 1위 달성. 공매도 세력에 대한 경계와 함께 긍정적 추세 전환 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공매도', '거래량', '적정주가']</t>
+          <t>['자사주 매입', '수익률', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>035720</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>64000</v>
+        <v>30325</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.89%</t>
+          <t>'+2.80%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.57</v>
+        <v>-0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F14" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="G14" t="n">
-        <v>463</v>
+        <v>336</v>
       </c>
       <c r="H14" t="n">
-        <v>41.01</v>
+        <v>28.81</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>62200</v>
+        <v>29500</v>
       </c>
       <c r="K14" t="n">
-        <v>63000</v>
+        <v>29900</v>
       </c>
       <c r="L14" t="n">
-        <v>64500</v>
+        <v>30650</v>
       </c>
       <c r="M14" t="n">
-        <v>62200</v>
+        <v>29900</v>
       </c>
       <c r="N14" t="n">
-        <v>40.44</v>
+        <v>28.82</v>
       </c>
       <c r="O14" t="n">
-        <v>146006083100</v>
+        <v>23211985725</v>
       </c>
       <c r="P14" t="n">
-        <v>67300</v>
+        <v>69700</v>
       </c>
       <c r="Q14" t="n">
-        <v>23150</v>
+        <v>29200</v>
       </c>
       <c r="R14" t="n">
-        <v>337000</v>
+        <v>120000</v>
       </c>
       <c r="S14" t="n">
-        <v>18000</v>
+        <v>14000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>삼성E&amp;A 코스피 수익률 1위 달성 및 자사주 매입 지속. 공매도 세력에 대한 경고와 함께 추세 전환 전망 제시.</t>
+          <t>물타기 및 공매도에 대한 언급이 있으나, 네이버 대비 열위적인 평가와 재료 부재에 대한 부정적 전망이 주를 이룸. 주가 반등에도 불구하고 3만원 이하 예상.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['자사주매입', '수익률', '추세전환']</t>
+          <t>['물타기', '공매도', '적정 주가']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>035720</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2215</v>
+        <v>2205</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.07%</t>
+          <t>'+1.61%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.18</v>
       </c>
       <c r="E15" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F15" t="n">
         <v>35</v>
       </c>
       <c r="G15" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H15" t="n">
         <v>5.07</v>
@@ -1806,7 +1806,7 @@
         <v>4.89</v>
       </c>
       <c r="O15" t="n">
-        <v>42604376063</v>
+        <v>43145172644</v>
       </c>
       <c r="P15" t="n">
         <v>4980</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16390</v>
+        <v>16380</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-0.06%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G16" t="n">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="H16" t="n">
         <v>28.03</v>
@@ -1898,7 +1898,7 @@
         <v>27.96</v>
       </c>
       <c r="O16" t="n">
-        <v>30889760805</v>
+        <v>31778196345</v>
       </c>
       <c r="P16" t="n">
         <v>35350</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>삼성중공업, 수주 증가세에도 목표주가 하향 조정 및 주가 부진 지적. 외국인, 기관 매수세 속 관망세.</t>
+          <t>수주 물량 대비 주가 부진 지속. 애널리스트 목표주가 하향 및 공매도 의혹 제기.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['수주', '목표주가', '외국인매수']</t>
+          <t>['수주', '주가 부진', '공매도']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1958,13 +1958,13 @@
         <v>-0.03</v>
       </c>
       <c r="E17" t="n">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="F17" t="n">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G17" t="n">
-        <v>900</v>
+        <v>923</v>
       </c>
       <c r="H17" t="n">
         <v>10.31</v>
@@ -1990,7 +1990,7 @@
         <v>10.34</v>
       </c>
       <c r="O17" t="n">
-        <v>53182042350</v>
+        <v>54389238700</v>
       </c>
       <c r="P17" t="n">
         <v>154800</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14180</v>
+        <v>14170</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-1.87%</t>
+          <t>'-1.94%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F18" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G18" t="n">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="H18" t="n">
         <v>9.83</v>
@@ -2082,7 +2082,7 @@
         <v>10.02</v>
       </c>
       <c r="O18" t="n">
-        <v>42178223455</v>
+        <v>43215500600</v>
       </c>
       <c r="P18" t="n">
         <v>40350</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>대우건설 주가 조작 및 공매도 관련 강한 비판. 새 경영진에 대한 불신 및 주가 부진에 대한 불만 토로.</t>
+          <t>주가 조작 및 경영진에 대한 불신 심화. 부정적 여론 형성.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가조작', '공매도', '경영진']</t>
+          <t>['주가 조작', '경영진', '불신']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1997</v>
+        <v>2005</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-4.22%</t>
+          <t>'-3.84%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.39</v>
       </c>
       <c r="E19" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F19" t="n">
         <v>55</v>
       </c>
       <c r="G19" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H19" t="n">
         <v>2.52</v>
@@ -2174,7 +2174,7 @@
         <v>2.13</v>
       </c>
       <c r="O19" t="n">
-        <v>13236241961</v>
+        <v>13338570862</v>
       </c>
       <c r="P19" t="n">
         <v>6190</v>

--- a/data/trending_integrated_20261028_11.xlsx
+++ b/data/trending_integrated_20261028_11.xlsx
@@ -581,7 +581,7 @@
         <v>105</v>
       </c>
       <c r="F2" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G2" t="n">
         <v>212</v>
@@ -610,7 +610,7 @@
         <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>148610426776</v>
+        <v>148889155161</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29100</v>
+        <v>29050</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.53%</t>
+          <t>'+22.32%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -702,7 +702,7 @@
         <v>5.31</v>
       </c>
       <c r="O3" t="n">
-        <v>140333045850</v>
+        <v>141351057000</v>
       </c>
       <c r="P3" t="n">
         <v>50600</v>
@@ -762,13 +762,13 @@
         <v>0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F4" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G4" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H4" t="n">
         <v>1.42</v>
@@ -785,7 +785,7 @@
         <v>8230</v>
       </c>
       <c r="L4" t="n">
-        <v>9290</v>
+        <v>9350</v>
       </c>
       <c r="M4" t="n">
         <v>8100</v>
@@ -794,7 +794,7 @@
         <v>1.15</v>
       </c>
       <c r="O4" t="n">
-        <v>75490453450</v>
+        <v>80745398180</v>
       </c>
       <c r="P4" t="n">
         <v>9820</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17580</v>
+        <v>17630</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.05%</t>
+          <t>'+11.37%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>121</v>
       </c>
       <c r="F5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G5" t="n">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="H5" t="n">
         <v>1.11</v>
@@ -886,7 +886,7 @@
         <v>0.09</v>
       </c>
       <c r="O5" t="n">
-        <v>204744956620</v>
+        <v>206734596660</v>
       </c>
       <c r="P5" t="n">
         <v>28800</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>187300</v>
+        <v>188100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.47%</t>
+          <t>'+9.94%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>49</v>
       </c>
       <c r="G6" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H6" t="n">
         <v>74.90000000000001</v>
@@ -978,7 +978,7 @@
         <v>74.89</v>
       </c>
       <c r="O6" t="n">
-        <v>509577638150</v>
+        <v>516891437050</v>
       </c>
       <c r="P6" t="n">
         <v>243500</v>
@@ -1023,83 +1023,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>나무가</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18600</v>
+        <v>1465000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.84%</t>
+          <t>'+9.25%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.61</v>
+        <v>-0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>116</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>64</v>
+        <v>508</v>
       </c>
       <c r="G7" t="n">
-        <v>308</v>
+        <v>1841</v>
       </c>
       <c r="H7" t="n">
-        <v>4.74</v>
+        <v>48.61</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>17090</v>
+        <v>1341000</v>
       </c>
       <c r="K7" t="n">
-        <v>19270</v>
+        <v>1390000</v>
       </c>
       <c r="L7" t="n">
-        <v>20450</v>
+        <v>1467000</v>
       </c>
       <c r="M7" t="n">
-        <v>18070</v>
+        <v>1358000</v>
       </c>
       <c r="N7" t="n">
-        <v>4.13</v>
+        <v>48.66</v>
       </c>
       <c r="O7" t="n">
-        <v>39629446480</v>
+        <v>3221617150500</v>
       </c>
       <c r="P7" t="n">
-        <v>28600</v>
+        <v>2987000</v>
       </c>
       <c r="Q7" t="n">
-        <v>11050</v>
+        <v>501000</v>
       </c>
       <c r="R7" t="n">
-        <v>-34000</v>
+        <v>53000</v>
       </c>
       <c r="S7" t="n">
-        <v>9000</v>
+        <v>55000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>아틀라스 휴머노이드 발주 및 로봇 사업 확장 기대. 카메라 모듈 공급 및 높은 이익률 기반 주가 상승 전망.</t>
+          <t>2029년 완판 소식과 20조원 규모 자사주 매입 발표에 힘입어 반도체 업황 불신 해소 및 주가 상승 전망이 우세합니다.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['휴머노이드', '로봇', '카메라 모듈']</t>
+          <t>['자사주 매입', '반도체 업황', '완판']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>190510</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14880</v>
+        <v>14900</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.61%</t>
+          <t>'+8.76%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="F8" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G8" t="n">
-        <v>416</v>
+        <v>442</v>
       </c>
       <c r="H8" t="n">
         <v>2.87</v>
@@ -1162,7 +1162,7 @@
         <v>2.82</v>
       </c>
       <c r="O8" t="n">
-        <v>141217623325</v>
+        <v>144421509650</v>
       </c>
       <c r="P8" t="n">
         <v>31500</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>메타 유리 기판 및 해상 광통신 케이블 사업 기대감. 외국인 프로그램 매수세 유입 및 공매도 세력 압박.</t>
+          <t>메타 유리기판, 해상광통신 케이블 관련 모멘텀 및 외인 프로그램 매수세 유입으로 2만원 돌파 및 대세 상승 전망이 강하게 제기됩니다.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['유리 기판', '광통신', '외국인 매수']</t>
+          <t>['유리기판', '해상광통신', '프로그램 매수']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1452000</v>
+        <v>241000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.28%</t>
+          <t>'+8.56%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="E9" t="n">
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>501</v>
+        <v>485</v>
       </c>
       <c r="G9" t="n">
-        <v>1837</v>
+        <v>1788</v>
       </c>
       <c r="H9" t="n">
-        <v>48.61</v>
+        <v>46.15</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,47 +1239,47 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1341000</v>
+        <v>222000</v>
       </c>
       <c r="K9" t="n">
-        <v>1390000</v>
+        <v>231000</v>
       </c>
       <c r="L9" t="n">
-        <v>1467000</v>
+        <v>243000</v>
       </c>
       <c r="M9" t="n">
-        <v>1358000</v>
+        <v>228000</v>
       </c>
       <c r="N9" t="n">
-        <v>48.66</v>
+        <v>46.1</v>
       </c>
       <c r="O9" t="n">
-        <v>3156467447500</v>
+        <v>2171904363750</v>
       </c>
       <c r="P9" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>501000</v>
+        <v>94500</v>
       </c>
       <c r="R9" t="n">
-        <v>53000</v>
+        <v>1304000</v>
       </c>
       <c r="S9" t="n">
-        <v>55000</v>
+        <v>524000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>29년까지 HBM 완판 전망 및 자사주 20조 취득 발표. 반도체 업황 호조에 따른 주가 상승 기대감 고조.</t>
+          <t>차기 대선 관련 언급이 혼재된 가운데, HBM4 점유율 및 연말 목표 주가 30 등에 대한 긍정적 전망이 일부 존재합니다.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['HBM', '자사주 매입', '반도체 업황']</t>
+          <t>['HBM4', '점유율', '목표 주가']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>나무가</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>239500</v>
+        <v>18500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+7.88%</t>
+          <t>'+8.25%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.05</v>
+        <v>0.61</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>115</v>
       </c>
       <c r="F10" t="n">
-        <v>484</v>
+        <v>62</v>
       </c>
       <c r="G10" t="n">
-        <v>1821</v>
+        <v>311</v>
       </c>
       <c r="H10" t="n">
-        <v>46.15</v>
+        <v>4.74</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>222000</v>
+        <v>17090</v>
       </c>
       <c r="K10" t="n">
-        <v>231000</v>
+        <v>19270</v>
       </c>
       <c r="L10" t="n">
-        <v>243000</v>
+        <v>20450</v>
       </c>
       <c r="M10" t="n">
-        <v>228000</v>
+        <v>18070</v>
       </c>
       <c r="N10" t="n">
-        <v>46.1</v>
+        <v>4.13</v>
       </c>
       <c r="O10" t="n">
-        <v>2097307612750</v>
+        <v>40071548230</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>28600</v>
       </c>
       <c r="Q10" t="n">
-        <v>94500</v>
+        <v>11050</v>
       </c>
       <c r="R10" t="n">
-        <v>1304000</v>
+        <v>-34000</v>
       </c>
       <c r="S10" t="n">
-        <v>524000</v>
+        <v>9000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>AI HBM4 점유율 경쟁 및 반도체 업황 호조 전망. 시장 참여자들의 긍정적 기대감 형성.</t>
+          <t>아틀라스 1만대 발주, 휴머노이드 폭등, 현대차 로봇 투자 등에 힘입어 삼성, 구글, 현대차 다음으로 주목받는 로봇주로 부각됩니다.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['HBM4', 'AI', '반도체']</t>
+          <t>['아틀라스', '휴머노이드', '로봇주']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>190510</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2600</v>
+        <v>2605</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+6.12%</t>
+          <t>'+6.33%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.68</v>
       </c>
       <c r="E11" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F11" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G11" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="H11" t="n">
         <v>1.69</v>
@@ -1438,7 +1438,7 @@
         <v>1.01</v>
       </c>
       <c r="O11" t="n">
-        <v>69318369462</v>
+        <v>70111217534</v>
       </c>
       <c r="P11" t="n">
         <v>2965</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>개인 물량 흡수 및 거래량 증가. 주가 상승 전환 가능성 언급.</t>
+          <t>개인 물량 흡수 및 계단식 하락 후 반등 기대감이 있으나, 음봉 마감 및 전환사채 전환 관련 불확실성도 존재합니다.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['개인 물량', '거래량', '주가 상승']</t>
+          <t>['개인 물량', '계단식 하락', '전환사채']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>182200</v>
+        <v>182400</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+4.53%</t>
+          <t>'+4.65%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="F12" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G12" t="n">
-        <v>1497</v>
+        <v>1527</v>
       </c>
       <c r="H12" t="n">
         <v>35.43</v>
@@ -1530,7 +1530,7 @@
         <v>35.49</v>
       </c>
       <c r="O12" t="n">
-        <v>106299580300</v>
+        <v>109627654200</v>
       </c>
       <c r="P12" t="n">
         <v>304000</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>프로그램 매수세와 야간 선물 상승에도 불구하고, 공매도 비율에 대한 우려와 기대감 없는 3행시가 제시됨. 외인 비중은 소폭 하락.</t>
+          <t>코어위브 상승 대비 낮은 주가 움직임, 신한 금융투자 매도세, 공매도 비율 등에 대한 불만이 제기되며 지수 대비 소외되는 모습입니다.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['공매도', '프로그램 매수', '야간 선물']</t>
+          <t>['코어위브', '공매도 비율', '신한 금융투자']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1590,13 +1590,13 @@
         <v>0.57</v>
       </c>
       <c r="E13" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G13" t="n">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="H13" t="n">
         <v>41.01</v>
@@ -1622,7 +1622,7 @@
         <v>40.44</v>
       </c>
       <c r="O13" t="n">
-        <v>150949424800</v>
+        <v>158095711650</v>
       </c>
       <c r="P13" t="n">
         <v>67300</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30325</v>
+        <v>30350</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.80%</t>
+          <t>'+2.88%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F14" t="n">
         <v>66</v>
       </c>
       <c r="G14" t="n">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="H14" t="n">
         <v>28.81</v>
@@ -1714,7 +1714,7 @@
         <v>28.82</v>
       </c>
       <c r="O14" t="n">
-        <v>23211985725</v>
+        <v>23551830150</v>
       </c>
       <c r="P14" t="n">
         <v>69700</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>물타기 및 공매도에 대한 언급이 있으나, 네이버 대비 열위적인 평가와 재료 부재에 대한 부정적 전망이 주를 이룸. 주가 반등에도 불구하고 3만원 이하 예상.</t>
+          <t>거래량 부진, 부정적 주가 흐름, 경영진 관련 부정적 언급으로 인해 3만원 이하 유지 및 추가 하락 가능성이 제기됩니다.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['물타기', '공매도', '적정 주가']</t>
+          <t>['거래량 부진', '주가 흐름', '경영진']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2205</v>
+        <v>2190</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.61%</t>
+          <t>'+0.92%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.18</v>
       </c>
       <c r="E15" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F15" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G15" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="H15" t="n">
         <v>5.07</v>
@@ -1806,7 +1806,7 @@
         <v>4.89</v>
       </c>
       <c r="O15" t="n">
-        <v>43145172644</v>
+        <v>43461367440</v>
       </c>
       <c r="P15" t="n">
         <v>4980</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16380</v>
+        <v>16440</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-0.06%</t>
+          <t>'+0.31%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G16" t="n">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="H16" t="n">
         <v>28.03</v>
@@ -1898,7 +1898,7 @@
         <v>27.96</v>
       </c>
       <c r="O16" t="n">
-        <v>31778196345</v>
+        <v>32633237455</v>
       </c>
       <c r="P16" t="n">
         <v>35350</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52100</v>
+        <v>52400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.70%</t>
+          <t>'-1.13%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.03</v>
       </c>
       <c r="E17" t="n">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F17" t="n">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="G17" t="n">
-        <v>923</v>
+        <v>949</v>
       </c>
       <c r="H17" t="n">
         <v>10.31</v>
@@ -1990,7 +1990,7 @@
         <v>10.34</v>
       </c>
       <c r="O17" t="n">
-        <v>54389238700</v>
+        <v>55680452650</v>
       </c>
       <c r="P17" t="n">
         <v>154800</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>한화오션, 코스피 지수 상승에도 불구하고 주가 하락. 외국인 매도세 및 공매도에 대한 불만 표출.</t>
+          <t>대세 상승 전환 전망에도 불구하고 2분기 실적 부진, 외국인 매도, 미국 조선업 협력 난항 등으로 인한 부정적 언급이 많습니다.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주가하락', '외국인매도', '공매도']</t>
+          <t>['실적 부진', '외국인 매도', '조선업 협력']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14170</v>
+        <v>14190</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-1.94%</t>
+          <t>'-1.80%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F18" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G18" t="n">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="H18" t="n">
         <v>9.83</v>
@@ -2082,7 +2082,7 @@
         <v>10.02</v>
       </c>
       <c r="O18" t="n">
-        <v>43215500600</v>
+        <v>44107010715</v>
       </c>
       <c r="P18" t="n">
         <v>40350</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>주가 조작 및 경영진에 대한 불신 심화. 부정적 여론 형성.</t>
+          <t>주가 조작 및 상폐 가능성, 경영진에 대한 불신이 주를 이루며, 타 건설주와의 비교를 통해 부정적 전망이 나타납니다.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가 조작', '경영진', '불신']</t>
+          <t>['주가 조작', '상폐', '경영진']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2005</v>
+        <v>2010</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.84%</t>
+          <t>'-3.60%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.39</v>
       </c>
       <c r="E19" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F19" t="n">
         <v>55</v>
       </c>
       <c r="G19" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H19" t="n">
         <v>2.52</v>
@@ -2174,7 +2174,7 @@
         <v>2.13</v>
       </c>
       <c r="O19" t="n">
-        <v>13338570862</v>
+        <v>13566355817</v>
       </c>
       <c r="P19" t="n">
         <v>6190</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>SK하이닉스 자사주 매입 공동 중개 호재에도 주가 하락. 액면병합 및 공매도 관련 우려 제기.</t>
+          <t>SK하이닉스 관련 호재 언급과 함께 액면병합 가격 및 지수 대비 낮은 주가 움직임에 대한 의문이 제기됩니다.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['자사주매입', '공매도', '액면병합']</t>
+          <t>['액면병합', '자사주 매입', '공매']</t>
         </is>
       </c>
       <c r="X19" t="n">
